--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB506D9F-BCD8-2D4B-8C3C-C296C919B440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C219256-79C1-594F-BFF2-9CA5DFD4BEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="10560" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1480" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -248,6 +248,18 @@
   </si>
   <si>
     <t>IsR5Ed7uivE</t>
+  </si>
+  <si>
+    <t>3pV192wNOls</t>
+  </si>
+  <si>
+    <t>02-Summarizing_Data</t>
+  </si>
+  <si>
+    <t>5:00 pm</t>
+  </si>
+  <si>
+    <t>6:00 pm</t>
   </si>
 </sst>
 </file>
@@ -760,7 +772,12 @@
       <c r="E5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -789,10 +806,10 @@
         <v>46293</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C219256-79C1-594F-BFF2-9CA5DFD4BEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B246EE3B-8AF5-8C4B-AAB0-51221D104384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1100" yWindow="9840" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
   <si>
     <t>Date</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>6:00 pm</t>
+  </si>
+  <si>
+    <t>03-Probability</t>
+  </si>
+  <si>
+    <t>ox5LcZYFbPM</t>
   </si>
 </sst>
 </file>
@@ -797,7 +803,12 @@
       <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
+      </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B246EE3B-8AF5-8C4B-AAB0-51221D104384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E51BBB-C771-BB4F-9B1B-DB2F79FDC7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="9840" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1100" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>ox5LcZYFbPM</t>
+  </si>
+  <si>
+    <t>04-Distributions</t>
+  </si>
+  <si>
+    <t>oAh91T5Ewsk</t>
   </si>
 </sst>
 </file>
@@ -828,6 +834,12 @@
       <c r="E7" t="s">
         <v>44</v>
       </c>
+      <c r="F7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E51BBB-C771-BB4F-9B1B-DB2F79FDC7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893DC6CB-7CD5-3342-B829-CD59CD11D744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>oAh91T5Ewsk</t>
+  </si>
+  <si>
+    <t>05-Foundation_for_Inference</t>
+  </si>
+  <si>
+    <t>n79ANKM2-No</t>
   </si>
 </sst>
 </file>
@@ -859,6 +865,12 @@
       <c r="E8" t="s">
         <v>45</v>
       </c>
+      <c r="F8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s">
+        <v>79</v>
+      </c>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893DC6CB-7CD5-3342-B829-CD59CD11D744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E935B358-5056-AC44-B4CE-2FE44DA2CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>n79ANKM2-No</t>
+  </si>
+  <si>
+    <t>G6rQ6sCwPlI</t>
+  </si>
+  <si>
+    <t>06-Inference_for_Categorical_Data</t>
   </si>
 </sst>
 </file>
@@ -900,6 +906,12 @@
       <c r="E10" t="s">
         <v>46</v>
       </c>
+      <c r="F10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" t="s">
+        <v>82</v>
+      </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E935B358-5056-AC44-B4CE-2FE44DA2CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1156C5FD-8C57-DE46-9910-3D3B6DCAAC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>06-Inference_for_Categorical_Data</t>
+  </si>
+  <si>
+    <t>07-Inference_for_Numerical_Data</t>
   </si>
 </sst>
 </file>
@@ -931,6 +934,9 @@
       <c r="E11" t="s">
         <v>47</v>
       </c>
+      <c r="G11" t="s">
+        <v>83</v>
+      </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
